--- a/results/regression_output/robustness/eap_jackknife.xlsx
+++ b/results/regression_output/robustness/eap_jackknife.xlsx
@@ -492,10 +492,10 @@
         <v>-0.5950760110920711</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07595852059371841</v>
+        <v>0.06080434296142238</v>
       </c>
       <c r="H2" t="n">
-        <v>1.023625628704394e-13</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>330</v>
@@ -528,10 +528,10 @@
         <v>-0.4174116862696374</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08843968337813951</v>
+        <v>0.04036089931017466</v>
       </c>
       <c r="H3" t="n">
-        <v>3.815188350797527e-06</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>320</v>
@@ -564,10 +564,10 @@
         <v>-0.5480064673510834</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07069309587493026</v>
+        <v>0.05838386260929287</v>
       </c>
       <c r="H4" t="n">
-        <v>1.905142710256769e-13</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>320</v>
@@ -600,10 +600,10 @@
         <v>-0.6672792205539052</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08510036599004535</v>
+        <v>0.07354393725742847</v>
       </c>
       <c r="H5" t="n">
-        <v>1.072475441787901e-13</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>320</v>
@@ -636,10 +636,10 @@
         <v>-0.671715633285092</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08288435156181782</v>
+        <v>0.06751229714615256</v>
       </c>
       <c r="H6" t="n">
-        <v>1.909583602355269e-14</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>320</v>
@@ -672,10 +672,10 @@
         <v>-0.6036162744336258</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07710662557398199</v>
+        <v>0.06216151445097261</v>
       </c>
       <c r="H7" t="n">
-        <v>1.163513729807164e-13</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>320</v>
@@ -708,10 +708,10 @@
         <v>-0.6039648471403992</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07394756852400641</v>
+        <v>0.06924809951325482</v>
       </c>
       <c r="H8" t="n">
-        <v>1.265654248072678e-14</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="I8" t="n">
         <v>320</v>
